--- a/Nunn_etal_2001/Nunn_etal_2001_registry_rows.xlsx
+++ b/Nunn_etal_2001/Nunn_etal_2001_registry_rows.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source list" sheetId="1" r:id="Rdd6eda9aa1f140e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry_rows" sheetId="2" r:id="Rc6c51cb0c269485f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOW_TO_PASTE" sheetId="3" r:id="R3db51867770c43a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source list" sheetId="1" r:id="R000a89f1ce2c4f49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry_rows" sheetId="2" r:id="R627809f246744078"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOW_TO_PASTE" sheetId="3" r:id="R7ca098cec23c464b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -333,7 +333,7 @@
         <x:v>Group composition, adult sex ratio and group-size covariates</x:v>
       </x:c>
       <x:c r="C2" s="3" t="str">
-        <x:v>Source tables / results to select</x:v>
+        <x:v>Underlying group-composition database — not tabulated in this paper</x:v>
       </x:c>
       <x:c r="D2" s="3" t="str">
         <x:v>HOLD — resolve exact source and uncovered values
@@ -350,13 +350,13 @@
         <x:v>Nicholas Saddler dissertation: Methods, Table 2 note and References (local final dissertation). Kamilar_Cooper_2013 S2 reference table; corrected 2001 citation in source notes.</x:v>
       </x:c>
       <x:c r="H2" s="3" t="str">
-        <x:v>Unresolved — full text needed before assigning an item number</x:v>
+        <x:v>Underlying dataset unresolved — Full text verified. Methods, PDF p. 2 / printed p. 647, attributes adult male/female counts to an unpublished database and gives the historical faculty.virginia.edu/charlienunn address. Tables 1–2 on p. 650 concern cycling/swelling evidence, not the requested group-size values. Leave Item number blank until the underlying dataset or correct source is located; dissertation-source identity remains unresolved.</x:v>
       </x:c>
       <x:c r="I2" s="3" t="str">
-        <x:v>Full text not obtained — item cannot yet be verified</x:v>
+        <x:v>Existing full-text PDF verified in EndNote; original retained</x:v>
       </x:c>
       <x:c r="J2" s="3" t="str">
-        <x:v>Not obtained</x:v>
+        <x:v>/Users/crossmodal/Documents/References.Data/PDF/3829176142/Nunn-2001-Do exaggerated sexual swellings func.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -508,7 +508,7 @@
         <x:v>Human visual check of snapshot</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="190" customHeight="1">
+    <x:row r="2" ht="200" customHeight="1">
       <x:c r="A2" s="3" t="str">
         <x:v>Nunn, C. L., van Schaik, C. P., &amp; Zinner, D. (2001). Do exaggerated sexual swellings function in female mating competition in primates? A comparative test of the reliable indicator hypothesis. Behavioral Ecology, 12(5), 646–654. https://doi.org/10.1093/beheco/12.5.646</x:v>
       </x:c>
@@ -525,11 +525,11 @@
       <x:c r="L2" s="6"/>
       <x:c r="M2" s="6"/>
       <x:c r="N2" s="3" t="str">
-        <x:v>Article tables/figures/text (not extracted)</x:v>
+        <x:v>Existing EndNote full-text PDF verified; no dataset extraction</x:v>
       </x:c>
       <x:c r="O2" s="3" t="str">
         <x:v>Nick: explicit group-size source, incomplete citation. Planned folder: Nunn_etal_2001. Target: Source tables / results to select. Correct citation includes Zinner. Confirm the actual group-size source and observation unit before ingestion; overlap with existing socioecological compilations is unresolved.
-Item check 2026-10-25: Unresolved — full text needed before assigning an item number. Availability: Full text not obtained — item cannot yet be verified.</x:v>
+EndNote check 2026-10-25: Underlying dataset unresolved — Full text verified. Methods, PDF p. 2 / printed p. 647, attributes adult male/female counts to an unpublished database and gives the historical faculty.virginia.edu/charlienunn address. Tables 1–2 on p. 650 concern cycling/swelling evidence, not the requested group-size values. Leave Item number blank until the underlying dataset or correct source is located; dissertation-source identity remains unresolved. Local PDF: /Users/crossmodal/Documents/References.Data/PDF/3829176142/Nunn-2001-Do exaggerated sexual swellings func.pdf</x:v>
       </x:c>
       <x:c r="P2" s="3" t="str">
         <x:v>HOLD — resolve exact source and uncovered values</x:v>
@@ -550,7 +550,7 @@
         <x:v>Primates</x:v>
       </x:c>
       <x:c r="X2" s="3" t="str">
-        <x:v>Group composition, adult sex ratio and group-size covariates</x:v>
+        <x:v>Underlying group-composition database — not tabulated in this paper</x:v>
       </x:c>
       <x:c r="Y2" s="3"/>
       <x:c r="Z2" s="3"/>
@@ -697,7 +697,7 @@
         <x:v>Source files</x:v>
       </x:c>
       <x:c r="B14" s="3" t="str">
-        <x:v>Acquired PDFs, full-text HTML and original Kerney supplements are stored in /Users/crossmodal/Library/CloudStorage/OneDrive-AllenInstitute/Evo-M1-Trait-Data-restricted/source_library/Nick_Fran_2026-10-25. README.md in each source folder gives complete paths and verification details. Kowianski 1999 uses an existing PDF in the teaching archive.</x:v>
+        <x:v>EndNote PDFs are linked by full path in Source list and source-folder README files; originals remain unchanged. Earlier downloads remain in /Users/crossmodal/Library/CloudStorage/OneDrive-AllenInstitute/Evo-M1-Trait-Data-restricted/source_library/Nick_Fran_2026-10-25. Kowianski 1999 remains in the teaching archive. File availability does not establish new data.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="100" customHeight="1">
@@ -705,7 +705,7 @@
         <x:v>Unresolved items</x:v>
       </x:c>
       <x:c r="B15" s="3" t="str">
-        <x:v>Blank Item number means either full text is still required or a review is REFERENCE ONLY. Smaers 2013 Table 1 is retained from earlier identification but has not been reverified from a locally acquired full text. Human snapshot checks remain pending.</x:v>
+        <x:v>All 29 candidate full texts are now available. Blank Item number remains intentional for reference-only reviews and for Nunn 2001, whose group-composition input database is not printed in the paper. Results Text is a descriptive source locus, not a printed table number. No data extraction, deduplication or human snapshot check has been completed.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -989,13 +989,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B126845C-A22C-410E-80C0-410CE42A9A2C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6EFD8CA0-BCD2-48F5-B02E-FC230C65A9D9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C62940FF-F6FD-4C4E-8F40-14DD72158CD2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD7F65D6-46EE-4885-B3D9-7D3212923B4C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AAC7C65-A4CA-4CC9-800B-10752B489D26}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3207231A-5602-4335-9F34-40B2FE27DEF4}"/>
 </file>